--- a/data/trans_dic/P16A11-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 13,85</t>
+          <t>8,17; 14,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,49</t>
+          <t>12,93; 20,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,11</t>
+          <t>9,61; 16,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,81</t>
+          <t>17,54; 24,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 13,58</t>
+          <t>7,19; 13,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 12,72</t>
+          <t>5,91; 13,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,39</t>
+          <t>6,29; 13,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,96</t>
+          <t>9,22; 13,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 12,72</t>
+          <t>8,42; 12,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 16,18</t>
+          <t>10,8; 16,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 13,57</t>
+          <t>8,79; 13,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,1; 18,36</t>
+          <t>14,31; 18,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,63</t>
+          <t>9,84; 17,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,11; 16,58</t>
+          <t>10,14; 16,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 18,28</t>
+          <t>10,66; 18,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 24,47</t>
+          <t>17,54; 24,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,04</t>
+          <t>3,48; 8,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 13,36</t>
+          <t>6,33; 13,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,08</t>
+          <t>4,77; 10,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,05</t>
+          <t>10,07; 15,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,58</t>
+          <t>7,32; 11,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,12</t>
+          <t>9,22; 14,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,34</t>
+          <t>8,78; 13,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 19,13</t>
+          <t>14,82; 19,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,83</t>
+          <t>9,23; 14,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,58</t>
+          <t>17,97; 25,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 19,24</t>
+          <t>13,3; 19,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 22,15</t>
+          <t>4,97; 22,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,15</t>
+          <t>9,26; 19,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 27,92</t>
+          <t>17,24; 28,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,06; 28,12</t>
+          <t>14,82; 29,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 28,85</t>
+          <t>18,93; 28,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 14,74</t>
+          <t>9,85; 15,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,07; 24,9</t>
+          <t>18,71; 24,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 20,3</t>
+          <t>14,3; 20,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 22,61</t>
+          <t>6,51; 22,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 18,3</t>
+          <t>14,44; 18,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 20,98</t>
+          <t>16,21; 21,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 20,05</t>
+          <t>15,81; 20,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 23,56</t>
+          <t>19,06; 23,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 16,53</t>
+          <t>11,55; 16,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,2</t>
+          <t>8,5; 13,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 13,18</t>
+          <t>8,66; 13,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 64,01</t>
+          <t>15,15; 65,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 17,29</t>
+          <t>13,92; 17,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 17,14</t>
+          <t>13,7; 17,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 16,43</t>
+          <t>13,37; 16,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 50,63</t>
+          <t>18,37; 51,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 15,86</t>
+          <t>8,88; 15,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 21,87</t>
+          <t>14,88; 21,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 20,04</t>
+          <t>14,39; 20,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 23,59</t>
+          <t>16,45; 23,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 17,64</t>
+          <t>11,95; 18,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,05; 28,47</t>
+          <t>22,26; 28,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 22,9</t>
+          <t>16,4; 22,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,8; 28,46</t>
+          <t>18,52; 28,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 15,8</t>
+          <t>11,57; 16,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,1; 24,94</t>
+          <t>19,91; 24,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,42; 20,54</t>
+          <t>16,31; 20,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 25,57</t>
+          <t>18,54; 25,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,58</t>
+          <t>0,59; 3,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,76</t>
+          <t>0,38; 3,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,06</t>
+          <t>0,34; 3,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,1; 26,87</t>
+          <t>22,38; 27,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,82; 34,33</t>
+          <t>28,68; 34,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,71; 30,37</t>
+          <t>24,59; 30,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,73; 32,16</t>
+          <t>26,79; 32,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 22,14</t>
+          <t>18,27; 22,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 28,3</t>
+          <t>23,28; 28,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,46; 24,35</t>
+          <t>19,5; 24,43</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,48; 24,9</t>
+          <t>20,25; 24,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,77</t>
+          <t>11,56; 13,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,32; 18,01</t>
+          <t>15,45; 18,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,62; 16,07</t>
+          <t>13,73; 16,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,71; 19,82</t>
+          <t>13,74; 19,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,43; 17,92</t>
+          <t>15,4; 18,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,5; 22,4</t>
+          <t>19,53; 22,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,3; 19,04</t>
+          <t>16,36; 19,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,94; 39,06</t>
+          <t>19,98; 39,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,84; 15,54</t>
+          <t>13,76; 15,51</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,86; 19,74</t>
+          <t>17,94; 19,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,39; 17,26</t>
+          <t>15,36; 17,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,53; 30,33</t>
+          <t>18,68; 29,1</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38487; 65611</t>
+          <t>38714; 67082</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55401; 89591</t>
+          <t>56524; 90000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42235; 69133</t>
+          <t>41222; 69289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87403; 120310</t>
+          <t>88599; 122833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21264; 41636</t>
+          <t>22055; 42709</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18212; 39983</t>
+          <t>18572; 42348</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22230; 46472</t>
+          <t>21824; 48352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41839; 62476</t>
+          <t>41276; 61919</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63561; 99263</t>
+          <t>65721; 98086</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>80049; 121593</t>
+          <t>81188; 124021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67841; 105351</t>
+          <t>68225; 105900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134308; 174937</t>
+          <t>136360; 174423</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35847; 61010</t>
+          <t>36099; 63893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42151; 69140</t>
+          <t>42288; 70568</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41318; 68958</t>
+          <t>40220; 69309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77203; 110440</t>
+          <t>79181; 110721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13591; 33632</t>
+          <t>12954; 31276</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21328; 44806</t>
+          <t>21238; 46452</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17904; 41236</t>
+          <t>17764; 40801</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37817; 57579</t>
+          <t>38524; 58137</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53830; 85527</t>
+          <t>54083; 86025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71449; 106255</t>
+          <t>69370; 105768</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64726; 100010</t>
+          <t>65826; 100649</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123460; 159555</t>
+          <t>123585; 161252</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50252; 80438</t>
+          <t>50066; 78829</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110528; 154469</t>
+          <t>112918; 157051</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68694; 100401</t>
+          <t>69417; 102231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31836; 148034</t>
+          <t>33183; 150286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15961; 33800</t>
+          <t>15530; 32954</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44789; 71698</t>
+          <t>44262; 72125</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23364; 46716</t>
+          <t>24613; 48576</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31441; 48152</t>
+          <t>31598; 48146</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71035; 104703</t>
+          <t>69945; 107507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168830; 220387</t>
+          <t>165575; 217562</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98357; 139705</t>
+          <t>98415; 138614</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54661; 188865</t>
+          <t>54391; 188488</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>179478; 226633</t>
+          <t>178857; 229539</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>189244; 242921</t>
+          <t>187774; 245670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179555; 230516</t>
+          <t>181769; 233090</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>196957; 243798</t>
+          <t>197248; 244480</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83185; 118050</t>
+          <t>82509; 117695</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67400; 101179</t>
+          <t>65146; 101066</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71085; 108815</t>
+          <t>71525; 107696</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>147372; 625686</t>
+          <t>148109; 643615</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>273161; 337536</t>
+          <t>271886; 333236</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>266722; 329948</t>
+          <t>263760; 328421</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>262028; 324640</t>
+          <t>264143; 325378</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>372860; 1018769</t>
+          <t>369577; 1037668</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30247; 55436</t>
+          <t>31052; 55400</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75723; 111656</t>
+          <t>75978; 110956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88887; 124364</t>
+          <t>89334; 125035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80121; 111850</t>
+          <t>77964; 111577</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>65725; 100301</t>
+          <t>67954; 102704</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>167418; 216166</t>
+          <t>169032; 217922</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>123767; 169043</t>
+          <t>121072; 166124</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>149354; 238759</t>
+          <t>155355; 240366</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105846; 145124</t>
+          <t>106252; 148223</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>255291; 316675</t>
+          <t>252845; 314149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>223153; 279136</t>
+          <t>221618; 282641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>251881; 335695</t>
+          <t>243384; 331772</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1769; 10676</t>
+          <t>1769; 10432</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>996; 10006</t>
+          <t>1005; 9806</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6036</t>
+          <t>0; 5331</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>888; 7352</t>
+          <t>828; 7506</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>275919; 335540</t>
+          <t>279503; 337113</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>318851; 379797</t>
+          <t>317295; 381452</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>267371; 328583</t>
+          <t>266045; 331415</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>203211; 244452</t>
+          <t>203636; 243620</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>283430; 342547</t>
+          <t>282578; 348236</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321567; 388253</t>
+          <t>319479; 386224</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>266403; 333456</t>
+          <t>267019; 334448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>204952; 249119</t>
+          <t>202645; 249277</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>377788; 450248</t>
+          <t>377849; 452533</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>523494; 615583</t>
+          <t>528061; 620294</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>461185; 544036</t>
+          <t>464976; 547492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>462596; 668663</t>
+          <t>463724; 668754</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>521125; 605210</t>
+          <t>520147; 610948</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>689966; 792644</t>
+          <t>691203; 790671</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>575732; 672363</t>
+          <t>577915; 673124</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>712545; 1395965</t>
+          <t>714036; 1409344</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>919745; 1032662</t>
+          <t>914348; 1031247</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1241991; 1373300</t>
+          <t>1247986; 1380166</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1064385; 1193664</t>
+          <t>1062825; 1188548</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1287620; 2107594</t>
+          <t>1297587; 2021755</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A11-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A11-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,16</t>
+          <t>8,3; 14,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 20,59</t>
+          <t>12,92; 19,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,15</t>
+          <t>9,35; 16,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,31</t>
+          <t>17,0; 23,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 13,93</t>
+          <t>6,81; 13,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 13,47</t>
+          <t>6,1; 13,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 13,93</t>
+          <t>6,22; 13,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 13,84</t>
+          <t>9,85; 14,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 12,57</t>
+          <t>8,49; 12,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,5</t>
+          <t>10,66; 16,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,64</t>
+          <t>8,87; 13,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 18,31</t>
+          <t>14,43; 18,5</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,41</t>
+          <t>9,98; 17,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 16,92</t>
+          <t>10,22; 17,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 18,37</t>
+          <t>10,96; 18,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,54; 24,53</t>
+          <t>17,54; 24,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,41</t>
+          <t>3,53; 8,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 13,85</t>
+          <t>6,77; 13,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,96</t>
+          <t>4,84; 11,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 15,2</t>
+          <t>10,83; 16,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,64</t>
+          <t>7,44; 11,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,06</t>
+          <t>9,31; 14,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,43</t>
+          <t>8,67; 13,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,34</t>
+          <t>15,13; 19,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,53</t>
+          <t>9,16; 14,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 25,0</t>
+          <t>18,01; 24,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 19,59</t>
+          <t>13,1; 19,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 22,49</t>
+          <t>17,55; 24,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,26; 19,64</t>
+          <t>8,91; 20,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 28,08</t>
+          <t>17,63; 28,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,82; 29,24</t>
+          <t>14,22; 28,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 28,85</t>
+          <t>18,58; 27,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 15,14</t>
+          <t>10,0; 14,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 24,58</t>
+          <t>18,46; 24,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,3; 20,15</t>
+          <t>14,68; 20,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 22,57</t>
+          <t>18,73; 24,3</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 18,54</t>
+          <t>14,32; 18,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 21,21</t>
+          <t>16,28; 21,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 20,28</t>
+          <t>15,59; 20,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,06; 23,63</t>
+          <t>18,8; 23,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,55; 16,48</t>
+          <t>11,51; 16,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,18</t>
+          <t>8,56; 13,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 13,04</t>
+          <t>8,63; 13,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,15; 65,84</t>
+          <t>13,65; 17,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 17,07</t>
+          <t>13,92; 17,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 17,06</t>
+          <t>13,79; 17,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,47</t>
+          <t>13,44; 16,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 51,57</t>
+          <t>17,07; 20,21</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 15,85</t>
+          <t>8,75; 16,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,73</t>
+          <t>14,84; 21,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,39; 20,14</t>
+          <t>14,27; 20,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 23,54</t>
+          <t>15,64; 21,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 18,06</t>
+          <t>11,59; 17,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,26; 28,7</t>
+          <t>22,11; 28,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,4; 22,5</t>
+          <t>16,52; 22,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,52; 28,65</t>
+          <t>24,46; 29,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,57; 16,14</t>
+          <t>11,45; 16,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 24,74</t>
+          <t>20,02; 24,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,31; 20,8</t>
+          <t>16,54; 20,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 25,27</t>
+          <t>21,15; 25,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,5</t>
+          <t>0,58; 3,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,69</t>
+          <t>0,38; 3,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,12</t>
+          <t>0,4; 3,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,38; 27,0</t>
+          <t>22,37; 27,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,68; 34,48</t>
+          <t>28,9; 34,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,59; 30,63</t>
+          <t>24,85; 30,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,79; 32,05</t>
+          <t>25,95; 31,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,27; 22,51</t>
+          <t>18,1; 22,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,28; 28,15</t>
+          <t>23,28; 28,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,5; 24,43</t>
+          <t>19,63; 24,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,25; 24,91</t>
+          <t>20,57; 24,83</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,84</t>
+          <t>11,42; 13,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,45; 18,15</t>
+          <t>15,34; 18,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 16,17</t>
+          <t>13,6; 16,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,74; 19,82</t>
+          <t>17,68; 20,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,4; 18,09</t>
+          <t>15,39; 17,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,53; 22,34</t>
+          <t>19,53; 22,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 19,06</t>
+          <t>16,5; 19,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,98; 39,44</t>
+          <t>19,66; 21,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,76; 15,51</t>
+          <t>13,82; 15,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,94; 19,84</t>
+          <t>17,84; 19,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,36; 17,18</t>
+          <t>15,49; 17,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,68; 29,1</t>
+          <t>19,01; 20,74</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103428</t>
+          <t>109793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>59222</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>154275</t>
+          <t>169015</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38714; 67082</t>
+          <t>39320; 67496</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56524; 90000</t>
+          <t>56486; 87184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41222; 69289</t>
+          <t>40121; 69669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88599; 122833</t>
+          <t>93598; 127423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22055; 42709</t>
+          <t>20886; 41129</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18572; 42348</t>
+          <t>19169; 42867</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21824; 48352</t>
+          <t>21573; 46441</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41276; 61919</t>
+          <t>48085; 71410</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65721; 98086</t>
+          <t>66281; 99161</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81188; 124021</t>
+          <t>80151; 121062</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68225; 105900</t>
+          <t>68882; 106172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>136360; 174423</t>
+          <t>149922; 192183</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93459</t>
+          <t>100257</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47499</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>140958</t>
+          <t>156026</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36099; 63893</t>
+          <t>36621; 62364</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42288; 70568</t>
+          <t>42616; 71011</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40220; 69309</t>
+          <t>41358; 68533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79181; 110721</t>
+          <t>84602; 117785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12954; 31276</t>
+          <t>13142; 32731</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21238; 46452</t>
+          <t>22704; 46575</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17764; 40801</t>
+          <t>18029; 41623</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38524; 58137</t>
+          <t>45826; 67851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54083; 86025</t>
+          <t>54951; 87394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69370; 105768</t>
+          <t>70038; 106230</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65826; 100649</t>
+          <t>64962; 101258</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123585; 161252</t>
+          <t>137004; 178448</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>129004</t>
+          <t>140471</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>50066; 78829</t>
+          <t>49701; 80962</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112918; 157051</t>
+          <t>113185; 155245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69417; 102231</t>
+          <t>68393; 101423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33183; 150286</t>
+          <t>82756; 114503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15530; 32954</t>
+          <t>14955; 34047</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44262; 72125</t>
+          <t>45280; 73369</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24613; 48576</t>
+          <t>23631; 47326</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31598; 48146</t>
+          <t>34836; 52473</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69945; 107507</t>
+          <t>71037; 106209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>165575; 217562</t>
+          <t>163413; 216239</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98415; 138614</t>
+          <t>101004; 141372</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54391; 188488</t>
+          <t>123421; 160148</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220540</t>
+          <t>238429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>325968</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>546508</t>
+          <t>371496</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>178857; 229539</t>
+          <t>177326; 231269</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>187774; 245670</t>
+          <t>188494; 245937</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>181769; 233090</t>
+          <t>179233; 231819</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197248; 244480</t>
+          <t>212753; 265839</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>82509; 117695</t>
+          <t>82244; 119487</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65146; 101066</t>
+          <t>65616; 100258</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71525; 107696</t>
+          <t>71258; 109407</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>148109; 643615</t>
+          <t>117509; 149718</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>271886; 333236</t>
+          <t>271797; 333143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>263760; 328421</t>
+          <t>265348; 331075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>264143; 325378</t>
+          <t>265579; 326860</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>369577; 1037668</t>
+          <t>340072; 402593</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94128</t>
+          <t>103632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>206402</t>
+          <t>221940</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>300531</t>
+          <t>325572</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31052; 55400</t>
+          <t>30588; 55916</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75978; 110956</t>
+          <t>75766; 110816</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89334; 125035</t>
+          <t>88603; 125234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77964; 111577</t>
+          <t>88666; 121794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67954; 102704</t>
+          <t>65899; 101109</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>169032; 217922</t>
+          <t>167887; 214045</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>121072; 166124</t>
+          <t>121983; 167025</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>155355; 240366</t>
+          <t>203048; 244104</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>106252; 148223</t>
+          <t>105129; 148139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252845; 314149</t>
+          <t>254223; 314472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>221618; 282641</t>
+          <t>224707; 278076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>243384; 331772</t>
+          <t>295535; 351104</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>223465</t>
+          <t>241480</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>226346</t>
+          <t>244306</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1769; 10432</t>
+          <t>1743; 10999</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1005; 9806</t>
+          <t>1002; 9729</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 5639</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>828; 7506</t>
+          <t>940; 8101</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>279503; 337113</t>
+          <t>279327; 337935</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>317295; 381452</t>
+          <t>319687; 381532</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>266045; 331415</t>
+          <t>268879; 331302</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>203636; 243620</t>
+          <t>218793; 263810</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>282578; 348236</t>
+          <t>279991; 341166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319479; 386224</t>
+          <t>319423; 386823</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>267019; 334448</t>
+          <t>268725; 336577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>202645; 249277</t>
+          <t>222231; 268220</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>604492</t>
+          <t>651959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>893130</t>
+          <t>754928</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1497622</t>
+          <t>1406887</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>377849; 452533</t>
+          <t>373272; 450695</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>528061; 620294</t>
+          <t>524030; 616049</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>464976; 547492</t>
+          <t>460493; 546896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>463724; 668754</t>
+          <t>608416; 695865</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>520147; 610948</t>
+          <t>519828; 606409</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>691203; 790671</t>
+          <t>691066; 790862</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>577915; 673124</t>
+          <t>582835; 682429</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>714036; 1409344</t>
+          <t>714121; 794898</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>914348; 1031247</t>
+          <t>918358; 1032889</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1247986; 1380166</t>
+          <t>1241084; 1367020</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1062825; 1188548</t>
+          <t>1071286; 1196613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1297587; 2021755</t>
+          <t>1344765; 1466868</t>
         </is>
       </c>
     </row>
